--- a/lager-scanner/test/Lager_Test.xlsx
+++ b/lager-scanner/test/Lager_Test.xlsx
@@ -8,13 +8,16 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Materialliste" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stellplaetze" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Protokoll" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lageruebersicht" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PlanLayout" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lagerplan" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Verpackung" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stellplaetze" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Protokoll" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lageruebersicht" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PlanLayout" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lagerplan" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Verpackung'!$1:$1</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -190,22 +193,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblMaterial" displayName="tblMaterial" ref="A1:F51" headerRowCount="1">
-  <autoFilter ref="A1:F2"/>
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="tblMaterial" displayName="tblMaterial" ref="A1:D51" headerRowCount="1">
+  <autoFilter ref="A1:D2"/>
+  <tableColumns count="4">
     <tableColumn id="1" name="SAP"/>
     <tableColumn id="2" name="Bezeichnung"/>
     <tableColumn id="3" name="Lagerstand"/>
     <tableColumn id="4" name="Meldebestand"/>
-    <tableColumn id="5" name="StkProKarton"/>
-    <tableColumn id="6" name="StkProPalette"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblStellplatz" displayName="tblStellplatz" ref="A1:B201" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tblVerpackung" displayName="tblVerpackung" ref="A1:D51" headerRowCount="1">
+  <autoFilter ref="A1:D2"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="SAP"/>
+    <tableColumn id="2" name="Bezeichnung"/>
+    <tableColumn id="3" name="StkProPalette"/>
+    <tableColumn id="4" name="StkProKarton"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblStellplatz" displayName="tblStellplatz" ref="A1:B201" headerRowCount="1">
   <autoFilter ref="A1:B2"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Stellplatz"/>
@@ -215,8 +229,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="tblProtokoll" displayName="tblProtokoll" ref="A1:H2" headerRowCount="1">
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="tblProtokoll" displayName="tblProtokoll" ref="A1:H2" headerRowCount="1">
   <autoFilter ref="A1:H2"/>
   <tableColumns count="8">
     <tableColumn id="1" name="Zeit"/>
@@ -521,15 +535,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -553,16 +565,6 @@
           <t>Meldebestand</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>StkProKarton</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>StkProPalette</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -581,12 +583,6 @@
       <c r="D2" t="n">
         <v>480</v>
       </c>
-      <c r="E2" t="n">
-        <v>24</v>
-      </c>
-      <c r="F2" t="n">
-        <v>480</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -605,12 +601,6 @@
       <c r="D3" t="n">
         <v>240</v>
       </c>
-      <c r="E3" t="n">
-        <v>12</v>
-      </c>
-      <c r="F3" t="n">
-        <v>240</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -629,12 +619,6 @@
       <c r="D4" t="n">
         <v>1440</v>
       </c>
-      <c r="E4" t="n">
-        <v>24</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1440</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -653,12 +637,6 @@
       <c r="D5" t="n">
         <v>3000</v>
       </c>
-      <c r="E5" t="n">
-        <v>50</v>
-      </c>
-      <c r="F5" t="n">
-        <v>3000</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -677,12 +655,6 @@
       <c r="D6" t="n">
         <v>2000</v>
       </c>
-      <c r="E6" t="n">
-        <v>100</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2000</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -701,12 +673,6 @@
       <c r="D7" t="n">
         <v>30</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -725,12 +691,6 @@
       <c r="D8" t="n">
         <v>1000</v>
       </c>
-      <c r="E8" t="n">
-        <v>50</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1000</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -749,12 +709,6 @@
       <c r="D9" t="n">
         <v>120</v>
       </c>
-      <c r="E9" t="n">
-        <v>6</v>
-      </c>
-      <c r="F9" t="n">
-        <v>120</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -773,12 +727,6 @@
       <c r="D10" t="n">
         <v>1000</v>
       </c>
-      <c r="E10" t="n">
-        <v>50</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1000</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -797,12 +745,6 @@
       <c r="D11" t="n">
         <v>6000</v>
       </c>
-      <c r="E11" t="n">
-        <v>100</v>
-      </c>
-      <c r="F11" t="n">
-        <v>6000</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -821,12 +763,6 @@
       <c r="D12" t="n">
         <v>960</v>
       </c>
-      <c r="E12" t="n">
-        <v>24</v>
-      </c>
-      <c r="F12" t="n">
-        <v>960</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -845,12 +781,6 @@
       <c r="D13" t="n">
         <v>3000</v>
       </c>
-      <c r="E13" t="n">
-        <v>100</v>
-      </c>
-      <c r="F13" t="n">
-        <v>3000</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -869,12 +799,6 @@
       <c r="D14" t="n">
         <v>960</v>
       </c>
-      <c r="E14" t="n">
-        <v>24</v>
-      </c>
-      <c r="F14" t="n">
-        <v>960</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -893,12 +817,6 @@
       <c r="D15" t="n">
         <v>20</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>20</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -917,12 +835,6 @@
       <c r="D16" t="n">
         <v>360</v>
       </c>
-      <c r="E16" t="n">
-        <v>6</v>
-      </c>
-      <c r="F16" t="n">
-        <v>360</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -941,12 +853,6 @@
       <c r="D17" t="n">
         <v>40</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>40</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -965,12 +871,6 @@
       <c r="D18" t="n">
         <v>1440</v>
       </c>
-      <c r="E18" t="n">
-        <v>24</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1440</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -989,12 +889,6 @@
       <c r="D19" t="n">
         <v>480</v>
       </c>
-      <c r="E19" t="n">
-        <v>24</v>
-      </c>
-      <c r="F19" t="n">
-        <v>480</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1013,12 +907,6 @@
       <c r="D20" t="n">
         <v>3000</v>
       </c>
-      <c r="E20" t="n">
-        <v>50</v>
-      </c>
-      <c r="F20" t="n">
-        <v>3000</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1037,12 +925,6 @@
       <c r="D21" t="n">
         <v>240</v>
       </c>
-      <c r="E21" t="n">
-        <v>12</v>
-      </c>
-      <c r="F21" t="n">
-        <v>240</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1061,12 +943,6 @@
       <c r="D22" t="n">
         <v>1000</v>
       </c>
-      <c r="E22" t="n">
-        <v>50</v>
-      </c>
-      <c r="F22" t="n">
-        <v>1000</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1085,12 +961,6 @@
       <c r="D23" t="n">
         <v>360</v>
       </c>
-      <c r="E23" t="n">
-        <v>12</v>
-      </c>
-      <c r="F23" t="n">
-        <v>360</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1109,12 +979,6 @@
       <c r="D24" t="n">
         <v>480</v>
       </c>
-      <c r="E24" t="n">
-        <v>24</v>
-      </c>
-      <c r="F24" t="n">
-        <v>480</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1133,12 +997,6 @@
       <c r="D25" t="n">
         <v>2000</v>
       </c>
-      <c r="E25" t="n">
-        <v>50</v>
-      </c>
-      <c r="F25" t="n">
-        <v>2000</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1157,12 +1015,6 @@
       <c r="D26" t="n">
         <v>720</v>
       </c>
-      <c r="E26" t="n">
-        <v>12</v>
-      </c>
-      <c r="F26" t="n">
-        <v>720</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1181,12 +1033,6 @@
       <c r="D27" t="n">
         <v>120</v>
       </c>
-      <c r="E27" t="n">
-        <v>6</v>
-      </c>
-      <c r="F27" t="n">
-        <v>120</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1205,12 +1051,6 @@
       <c r="D28" t="n">
         <v>3000</v>
       </c>
-      <c r="E28" t="n">
-        <v>100</v>
-      </c>
-      <c r="F28" t="n">
-        <v>3000</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1229,12 +1069,6 @@
       <c r="D29" t="n">
         <v>240</v>
       </c>
-      <c r="E29" t="n">
-        <v>6</v>
-      </c>
-      <c r="F29" t="n">
-        <v>240</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1253,12 +1087,6 @@
       <c r="D30" t="n">
         <v>960</v>
       </c>
-      <c r="E30" t="n">
-        <v>24</v>
-      </c>
-      <c r="F30" t="n">
-        <v>960</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1277,12 +1105,6 @@
       <c r="D31" t="n">
         <v>1000</v>
       </c>
-      <c r="E31" t="n">
-        <v>50</v>
-      </c>
-      <c r="F31" t="n">
-        <v>1000</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1301,12 +1123,6 @@
       <c r="D32" t="n">
         <v>1440</v>
       </c>
-      <c r="E32" t="n">
-        <v>24</v>
-      </c>
-      <c r="F32" t="n">
-        <v>1440</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1325,12 +1141,6 @@
       <c r="D33" t="n">
         <v>480</v>
       </c>
-      <c r="E33" t="n">
-        <v>24</v>
-      </c>
-      <c r="F33" t="n">
-        <v>480</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1349,12 +1159,6 @@
       <c r="D34" t="n">
         <v>720</v>
       </c>
-      <c r="E34" t="n">
-        <v>24</v>
-      </c>
-      <c r="F34" t="n">
-        <v>720</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1373,12 +1177,6 @@
       <c r="D35" t="n">
         <v>20</v>
       </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>20</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1397,12 +1195,6 @@
       <c r="D36" t="n">
         <v>40</v>
       </c>
-      <c r="E36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" t="n">
-        <v>40</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1421,12 +1213,6 @@
       <c r="D37" t="n">
         <v>3000</v>
       </c>
-      <c r="E37" t="n">
-        <v>50</v>
-      </c>
-      <c r="F37" t="n">
-        <v>3000</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1445,12 +1231,6 @@
       <c r="D38" t="n">
         <v>2000</v>
       </c>
-      <c r="E38" t="n">
-        <v>50</v>
-      </c>
-      <c r="F38" t="n">
-        <v>2000</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1469,12 +1249,6 @@
       <c r="D39" t="n">
         <v>1440</v>
       </c>
-      <c r="E39" t="n">
-        <v>24</v>
-      </c>
-      <c r="F39" t="n">
-        <v>1440</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1493,12 +1267,6 @@
       <c r="D40" t="n">
         <v>30</v>
       </c>
-      <c r="E40" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" t="n">
-        <v>30</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1517,12 +1285,6 @@
       <c r="D41" t="n">
         <v>720</v>
       </c>
-      <c r="E41" t="n">
-        <v>24</v>
-      </c>
-      <c r="F41" t="n">
-        <v>720</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1541,12 +1303,6 @@
       <c r="D42" t="n">
         <v>360</v>
       </c>
-      <c r="E42" t="n">
-        <v>12</v>
-      </c>
-      <c r="F42" t="n">
-        <v>360</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1565,12 +1321,6 @@
       <c r="D43" t="n">
         <v>2000</v>
       </c>
-      <c r="E43" t="n">
-        <v>100</v>
-      </c>
-      <c r="F43" t="n">
-        <v>2000</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1589,12 +1339,6 @@
       <c r="D44" t="n">
         <v>240</v>
       </c>
-      <c r="E44" t="n">
-        <v>6</v>
-      </c>
-      <c r="F44" t="n">
-        <v>240</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1613,12 +1357,6 @@
       <c r="D45" t="n">
         <v>2000</v>
       </c>
-      <c r="E45" t="n">
-        <v>50</v>
-      </c>
-      <c r="F45" t="n">
-        <v>2000</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1637,12 +1375,6 @@
       <c r="D46" t="n">
         <v>720</v>
       </c>
-      <c r="E46" t="n">
-        <v>24</v>
-      </c>
-      <c r="F46" t="n">
-        <v>720</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1661,12 +1393,6 @@
       <c r="D47" t="n">
         <v>240</v>
       </c>
-      <c r="E47" t="n">
-        <v>12</v>
-      </c>
-      <c r="F47" t="n">
-        <v>240</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1685,12 +1411,6 @@
       <c r="D48" t="n">
         <v>360</v>
       </c>
-      <c r="E48" t="n">
-        <v>12</v>
-      </c>
-      <c r="F48" t="n">
-        <v>360</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1709,12 +1429,6 @@
       <c r="D49" t="n">
         <v>240</v>
       </c>
-      <c r="E49" t="n">
-        <v>12</v>
-      </c>
-      <c r="F49" t="n">
-        <v>240</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1733,12 +1447,6 @@
       <c r="D50" t="n">
         <v>720</v>
       </c>
-      <c r="E50" t="n">
-        <v>24</v>
-      </c>
-      <c r="F50" t="n">
-        <v>720</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1755,12 +1463,6 @@
         <v>4000</v>
       </c>
       <c r="D51" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E51" t="n">
-        <v>50</v>
-      </c>
-      <c r="F51" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -1773,6 +1475,952 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Bezeichnung</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>StkProPalette</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>StkProKarton</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>40290012</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Schraube M8x40 Typ A</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>480</v>
+      </c>
+      <c r="D2" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>40229779</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Mutter M8 Typ A</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>240</v>
+      </c>
+      <c r="D3" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>40211614</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Unterlegscheibe 8,4 Typ A</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D4" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>40214943</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabelbinder 200mm Typ A</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>40383028</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Folie 500mm Typ A</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>40381812</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Karton 600x400 Typ A</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>40287867</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Klebeband braun Typ A</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>40970777</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Etikett 100x50 Typ A</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>120</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>40227101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Dichtung DN50 Typ A</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D10" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>40734374</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Rohr 1/2 Zoll Typ A</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>40848628</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Winkel 90 Grad Typ A</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>960</v>
+      </c>
+      <c r="D12" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>40335070</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Scharnier 60mm Typ A</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D13" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>40775919</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Griff Edelstahl Typ A</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>960</v>
+      </c>
+      <c r="D14" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>40875717</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kleber 2K Typ A</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>20</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>40530530</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Palettenfolie Typ A</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>360</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>40951642</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Steckdose 3-fach Typ A</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>40</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>40866737</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabel 3x1,5 Typ A</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D18" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>40442533</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Schlauch 10mm Typ A</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>480</v>
+      </c>
+      <c r="D19" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>40926072</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Filter G4 Typ A</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D20" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>40957320</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Lager 6204 Typ A</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>240</v>
+      </c>
+      <c r="D21" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>40316823</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Schraube M8x40 Typ B</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D22" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>40370530</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Mutter M8 Typ B</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>360</v>
+      </c>
+      <c r="D23" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>40607519</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Unterlegscheibe 8,4 Typ B</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>480</v>
+      </c>
+      <c r="D24" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>40618359</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Kabelbinder 200mm Typ B</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D25" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>40808053</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Folie 500mm Typ B</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>720</v>
+      </c>
+      <c r="D26" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>40397233</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Karton 600x400 Typ B</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>120</v>
+      </c>
+      <c r="D27" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>40393478</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Klebeband braun Typ B</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D28" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>40858945</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Etikett 100x50 Typ B</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>240</v>
+      </c>
+      <c r="D29" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>40280530</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Dichtung DN50 Typ B</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>960</v>
+      </c>
+      <c r="D30" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>40983056</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Rohr 1/2 Zoll Typ B</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D31" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>40607428</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Winkel 90 Grad Typ B</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D32" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>40918889</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Scharnier 60mm Typ B</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>480</v>
+      </c>
+      <c r="D33" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>40362103</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Griff Edelstahl Typ B</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>720</v>
+      </c>
+      <c r="D34" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>40866571</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Kleber 2K Typ B</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>20</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>40783478</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Palettenfolie Typ B</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>40</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>40360530</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Steckdose 3-fach Typ B</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D37" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>40545132</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Kabel 3x1,5 Typ B</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D38" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>40243012</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Schlauch 10mm Typ B</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D39" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>40498927</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Filter G4 Typ B</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>30</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>40436613</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Lager 6204 Typ B</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>720</v>
+      </c>
+      <c r="D41" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>40774362</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Schraube M8x40 Typ C</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>360</v>
+      </c>
+      <c r="D42" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>40489652</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Mutter M8 Typ C</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D43" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>40560777</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unterlegscheibe 8,4 Typ C</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>240</v>
+      </c>
+      <c r="D44" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>40799725</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Kabelbinder 200mm Typ C</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D45" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>40404197</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Folie 500mm Typ C</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>720</v>
+      </c>
+      <c r="D46" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>40739480</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Karton 600x400 Typ C</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>240</v>
+      </c>
+      <c r="D47" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>40705577</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Klebeband braun Typ C</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>360</v>
+      </c>
+      <c r="D48" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>40548327</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Etikett 100x50 Typ C</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>240</v>
+      </c>
+      <c r="D49" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>40392673</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Dichtung DN50 Typ C</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>720</v>
+      </c>
+      <c r="D50" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>40710530</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Rohr 1/2 Zoll Typ C</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D51" t="n">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3285,7 +3933,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3355,7 +4003,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -29409,7 +30057,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -30080,7 +30728,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
